--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.17510238652031</v>
+        <v>2.14095413780955</v>
       </c>
       <c r="D2" t="n">
-        <v>13.56336131604907</v>
+        <v>2.204046213857974</v>
       </c>
       <c r="E2" t="n">
-        <v>12.86879909337178</v>
+        <v>2.091179852672915</v>
       </c>
       <c r="F2" t="n">
-        <v>12.63044637651174</v>
+        <v>2.052447536183158</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.37094430944951</v>
+        <v>3.960278450285545</v>
       </c>
       <c r="D3" t="n">
-        <v>24.16976132921735</v>
+        <v>3.92758621599782</v>
       </c>
       <c r="E3" t="n">
-        <v>12.86879909337178</v>
+        <v>2.091179852672915</v>
       </c>
       <c r="F3" t="n">
-        <v>12.63044637651174</v>
+        <v>2.052447536183158</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.53384573690136</v>
+        <v>7.88674993224647</v>
       </c>
       <c r="D4" t="n">
-        <v>48.13576429297655</v>
+        <v>7.822061697608689</v>
       </c>
       <c r="E4" t="n">
-        <v>12.86879909337178</v>
+        <v>2.091179852672915</v>
       </c>
       <c r="F4" t="n">
-        <v>12.63044637651174</v>
+        <v>2.052447536183158</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.17581932842475</v>
+        <v>4.091070640869022</v>
       </c>
       <c r="D5" t="n">
-        <v>24.83866486484537</v>
+        <v>4.036283040537374</v>
       </c>
       <c r="E5" t="n">
-        <v>12.86879909337178</v>
+        <v>2.091179852672915</v>
       </c>
       <c r="F5" t="n">
-        <v>12.63044637651174</v>
+        <v>2.052447536183158</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
